--- a/Test_Cases/05_Player/Weblink_Player_Test_Cases.xlsx
+++ b/Test_Cases/05_Player/Weblink_Player_Test_Cases.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,20 +432,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="78" customWidth="1" min="9" max="9"/>
-    <col width="78" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="84" customWidth="1" min="8" max="8"/>
+    <col width="82" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -799,8 +799,558 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Verify Weblink spinner is shown while page is loading</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Valid Weblink available.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Weblink</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Weblink.
+2. Observe while page loads.
+3. Wait for page load.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Loading spinner is visible during page load and clears when page appears.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Page remains loaded.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Verify stored Weblink is resolved before page is loaded</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Stored URL resolution</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Weblink resource stores a valid address.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Stored Weblink</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Weblink.
+2. Monitor resolution/load sequence.
+3. Observe loaded page.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Stored link is fetched/resolved before the external page is loaded.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Correct stored page is displayed.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Verify current stored Weblink is loaded instead of a previous cached link</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Correct resource</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Two Weblink resources point to different pages.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Two different Weblinks</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Weblink A.
+2. Close it.
+3. Open Weblink B.
+4. Observe page.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Weblink B loads its own stored page, not cached content from A.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Correct page is displayed.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Verify links and controls inside Weblink respond</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Page interaction</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>External page permits interaction.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Interactive webpage</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Weblink.
+2. Click supported links/controls.
+3. Observe page.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Page controls respond normally when Select interaction is active.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Webpage remains usable.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Verify Pan tool prevents interaction with framed page</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Pan interaction</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Weblink is open.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Weblink</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1. Select Pan.
+2. Try interacting with page.
+3. Select Select/another tool.
+4. Try interaction again.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Pan disables page interaction for board dragging; another tool restores it.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Interaction matches tool state.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Verify annotations remain fixed while page content scrolls</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Annotation alignment</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Weblink page supports scrolling; annotation available.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Scrollable webpage</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1. Draw annotation.
+2. Scroll inside page.
+3. Observe annotation.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Annotation remains attached to the player overlay rather than scrolling with page content.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Annotation remains aligned with player.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Verify clearing annotations keeps Weblink loaded</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Clear annotation</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Weblink has annotation.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Weblink</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1. Draw annotation.
+2. Clear annotations.
+3. Observe webpage.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Annotations are removed and webpage remains loaded.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Weblink remains open.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Verify closing Weblink from Playlist closes player</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Playlist close</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Weblink player open.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Weblink</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Weblink.
+2. Close corresponding resource from Playlist.
+3. Observe canvas.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Same Weblink Player closes.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Weblink is removed.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Verify unreachable Weblink does not leave spinner indefinitely</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Unreachable URL</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Unreachable test URL available.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Invalid/unreachable URL</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Weblink.
+2. Wait for page failure.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Player handles unreachable page without an indefinite spinner.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Failure is visible.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC-WEB-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Verify site that refuses framing leaves player open without crashing</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Frame restriction</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Test site refuses iframe embedding.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Frame-blocked site</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Weblink.
+2. Observe iframe.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Player remains open with blank/blocked frame rather than crashing the Whiteboard.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Whiteboard remains usable.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -811,17 +1361,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -976,8 +1526,228 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC-WEB-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Verify Weblink spinner is shown while page is loading</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC-WEB-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Verify stored Weblink is resolved before page is loaded</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC-WEB-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Verify current stored Weblink is loaded instead of a previous cached link</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC-WEB-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Verify links and controls inside Weblink respond</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC-WEB-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Verify Pan tool prevents interaction with framed page</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC-WEB-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Verify annotations remain fixed while page content scrolls</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC-WEB-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Verify clearing annotations keeps Weblink loaded</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC-WEB-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Verify closing Weblink from Playlist closes player</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC-WEB-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Verify unreachable Weblink does not leave spinner indefinitely</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC-WEB-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Verify site that refuses framing leaves player open without crashing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>